--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_UnCiv_003.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_UnCiv_003.xlsx
@@ -59,10 +59,10 @@
     <t>Formula</t>
   </si>
   <si>
-    <t>193-quater.1</t>
-  </si>
-  <si>
-    <t>193-quinquies.1</t>
+    <t>193-quater.2</t>
+  </si>
+  <si>
+    <t>193-quinquies.2</t>
   </si>
   <si>
     <t>194</t>
@@ -182,7 +182,7 @@
     <t>dataComunicazione</t>
   </si>
   <si>
-    <t>193-quinquies.1,193-quater.1</t>
+    <t>193-quater.2,193-quinquies.2</t>
   </si>
   <si>
     <t>Tipo atto da trascrivere</t>
@@ -3610,7 +3610,7 @@
         <v>180</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>28</v>
@@ -3702,7 +3702,7 @@
         <v>70</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>28</v>
@@ -3748,7 +3748,7 @@
         <v>74</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>28</v>
@@ -3771,7 +3771,7 @@
         <v>76</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>28</v>
@@ -3863,7 +3863,7 @@
         <v>84</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>28</v>
@@ -3909,7 +3909,7 @@
         <v>88</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>28</v>
@@ -3932,7 +3932,7 @@
         <v>89</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>28</v>
@@ -4001,7 +4001,7 @@
         <v>95</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>28</v>
@@ -4024,7 +4024,7 @@
         <v>97</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>28</v>
@@ -4070,7 +4070,7 @@
         <v>101</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>28</v>
@@ -4116,7 +4116,7 @@
         <v>105</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>28</v>
@@ -4162,7 +4162,7 @@
         <v>109</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>28</v>
@@ -4185,7 +4185,7 @@
         <v>111</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>28</v>
@@ -4254,7 +4254,7 @@
         <v>117</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>28</v>
